--- a/Server/Common/GameDatasheet/Original_Quest.xlsx
+++ b/Server/Common/GameDatasheet/Original_Quest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zmwps\Desktop\Project_MMORPG\Server\Common\GameDatasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2720F46-9DA6-4423-96AC-10A631A14C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948EC259-A812-4ACC-B2AD-1BE4E09DCD10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -132,9 +132,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"type": "kill", "object_id": 5000, "Count": 10}</t>
-  </si>
-  <si>
     <t>{"exp": 100, "gold": 200, "items": [{"id": 2000, "quantity": 3}]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -149,38 +146,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"type": "kill", "object_id": 5001, "Count": 10}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"type": "kill", "object_id": 5002, "Count": 10}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"type": "kill", "object_id": 5003, "Count": 10}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"type": "kill", "object_id": 5004, "Count": 10}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"type": "kill", "object_id": 5005, "Count": 10}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"type": "kill", "object_id": 5006, "Count": 10}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"type": "kill", "object_id": 5007, "Count": 10}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"type": "kill", "object_id": 5008, "Count": 10}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{"exp": 500, "gold": 200, "items": [{"id": 2000, "quantity": 6}]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -203,6 +168,33 @@
   <si>
     <t>{"exp": 1000, "gold": 200, "items": [{"id": 2000, "quantity": 11}]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"type": "kill", "template_id": 5000, "count": 10}</t>
+  </si>
+  <si>
+    <t>{"type": "kill", "template_id": 5001, "count": 10}</t>
+  </si>
+  <si>
+    <t>{"type": "kill", "template_id": 5002, "count": 10}</t>
+  </si>
+  <si>
+    <t>{"type": "kill", "template_id": 5003, "count": 10}</t>
+  </si>
+  <si>
+    <t>{"type": "kill", "template_id": 5004, "count": 10}</t>
+  </si>
+  <si>
+    <t>{"type": "kill", "template_id": 5005, "count": 10}</t>
+  </si>
+  <si>
+    <t>{"type": "kill", "template_id": 5006, "count": 10}</t>
+  </si>
+  <si>
+    <t>{"type": "kill", "template_id": 5007, "count": 10}</t>
+  </si>
+  <si>
+    <t>{"type": "kill", "template_id": 5008, "count": 10}</t>
   </si>
 </sst>
 </file>
@@ -585,7 +577,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -667,10 +659,10 @@
         <v>101</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>7</v>
@@ -699,10 +691,10 @@
         <v>101</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>7</v>
@@ -731,10 +723,10 @@
         <v>101</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>7</v>
@@ -763,10 +755,10 @@
         <v>101</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>7</v>
@@ -795,10 +787,10 @@
         <v>101</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>7</v>
@@ -827,10 +819,10 @@
         <v>101</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>7</v>
@@ -859,10 +851,10 @@
         <v>101</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>7</v>
@@ -891,10 +883,10 @@
         <v>101</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>7</v>
@@ -923,10 +915,10 @@
         <v>101</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>7</v>
